--- a/artfynd/A 319-2024 artfynd.xlsx
+++ b/artfynd/A 319-2024 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103398029</v>
+        <v>114555488</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Degerträsket västra, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811226.2234062217</v>
+        <v>811201</v>
       </c>
       <c r="R2" t="n">
-        <v>7317191.523855023</v>
+        <v>7317216</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +764,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Kristina  Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
+          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +779,7 @@
         <v>103398031</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811226.2234062217</v>
+        <v>811226</v>
       </c>
       <c r="R3" t="n">
-        <v>7317191.523855023</v>
+        <v>7317192</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -860,19 +844,9 @@
           <t>2022-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,60 +866,59 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Kristina  Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
+          <t>Amanda Tas, Kristina Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103398042</v>
+        <v>114555496</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Degerträsket västra, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811209.3588696608</v>
+        <v>811171</v>
       </c>
       <c r="R4" t="n">
-        <v>7317179.358919874</v>
+        <v>7317126</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +962,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas, Kristina  Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
+          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103398043</v>
+        <v>114555491</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Degerträsket västra, Nb</t>
+          <t>Norrbotten, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811226.2234062217</v>
+        <v>811206</v>
       </c>
       <c r="R5" t="n">
-        <v>7317191.523855023</v>
+        <v>7317215</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas, Kristina  Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
+          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1126,12 +1078,7 @@
         <v>114555492</v>
       </c>
       <c r="B6" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114555488</v>
+        <v>114555493</v>
       </c>
       <c r="B7" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1273,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811201</v>
+        <v>811232</v>
       </c>
       <c r="R7" t="n">
-        <v>7317216</v>
+        <v>7317180</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,37 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114555496</v>
+        <v>114555490</v>
       </c>
       <c r="B8" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1379,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811171</v>
+        <v>811226</v>
       </c>
       <c r="R8" t="n">
-        <v>7317126</v>
+        <v>7317180</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,15 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114555489</v>
+        <v>103398029</v>
       </c>
       <c r="B9" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,24 +1406,20 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Degerträsket västra, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811154</v>
+        <v>811226</v>
       </c>
       <c r="R9" t="n">
-        <v>7317167</v>
+        <v>7317192</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,12 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,27 +1463,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
+          <t>Amanda Tas, Kristina Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114555490</v>
+        <v>114555489</v>
       </c>
       <c r="B10" t="n">
-        <v>90726</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,21 +1486,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1591,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811226</v>
+        <v>811154</v>
       </c>
       <c r="R10" t="n">
-        <v>7317180</v>
+        <v>7317167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,37 +1576,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114555491</v>
+        <v>114555495</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1697,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811206</v>
+        <v>811218</v>
       </c>
       <c r="R11" t="n">
-        <v>7317215</v>
+        <v>7317197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,57 +1677,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114555493</v>
+        <v>103398042</v>
       </c>
       <c r="B12" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Degerträsket västra, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811232</v>
+        <v>811209</v>
       </c>
       <c r="R12" t="n">
-        <v>7317180</v>
+        <v>7317179</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,12 +1742,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,69 +1762,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
+          <t>Amanda Tas, Kristina Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>114555495</v>
+        <v>103398043</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norrbotten, Nb</t>
+          <t>Degerträsket västra, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811218</v>
+        <v>811226</v>
       </c>
       <c r="R13" t="n">
-        <v>7317197</v>
+        <v>7317192</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1939,12 +1839,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2022-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,12 +1859,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Mikael Andersson</t>
+          <t>Amanda Tas, Kristina Berglund, Sandra Selberg, Börrje Selberg, Erika Nordlund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 319-2024 artfynd.xlsx
+++ b/artfynd/A 319-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555488</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103398031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555496</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555491</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555492</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555493</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555490</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103398029</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555489</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114555495</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103398042</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,8 +1928,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103398043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>